--- a/DateBase/orders/Dang Nguyen48_2026-5-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-19.xlsx
@@ -520,6 +520,9 @@
       <c r="C11" t="str">
         <v>344_钢草_steal grass_Xanthorrhoea preissii Endl._1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -578,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0151520101055660</v>
+        <v>0151520101055662</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -521,12 +521,96 @@
         <v>344_钢草_steal grass_Xanthorrhoea preissii Endl._1bunch</v>
       </c>
       <c r="F11" t="str">
-        <v>2</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="C12" t="str" xml:space="preserve">
+        <v xml:space="preserve">405_小飞燕浅蓝_ delphinium ballkleid
+dark blue_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="C13" t="str" xml:space="preserve">
+        <v xml:space="preserve">499_小飞燕浅蓝_delphinium ballkleid
+light blue_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="C14" t="str" xml:space="preserve">
+        <v xml:space="preserve">404_小飞燕白色_ delphinium ballkleid
+white_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="C15" t="str" xml:space="preserve">
+        <v xml:space="preserve">497_小飞燕粉色_delphinium ballkleid
+pink_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>858_桔叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>623_多丁粉太子_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>624_多丁白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>3</v>
+      </c>
+      <c r="C20" t="str">
+        <v>653_大丽花 黑_undefined_undefined_5stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>651_大丽花 奶油桃子_undefined_undefined_5stems</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +665,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0151520101055662</v>
+        <v>0151520101055662055552051010100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-19.xlsx
@@ -607,6 +607,9 @@
       <c r="C21" t="str">
         <v>651_大丽花 奶油桃子_undefined_undefined_5stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -665,7 +668,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0151520101055662055552051010100</v>
+        <v>0151520101055662055552051010105</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -611,9 +611,89 @@
         <v>5</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>674_大丽花圣诞老人_undefined_undefined_5stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>533_风车果_scabiosa pods_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>559_粉廖_Polygonum_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>792_珍珠梅白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>4</v>
+      </c>
+      <c r="C26" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>420_松虫草QQ糖_scabiosa white pink_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>314_松虫草花边黑_scabiosa_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>793_珍珠梅粉_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -668,7 +748,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0151520101055662055552051010105</v>
+        <v>0151520101055662055552051010105510551515510100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-19.xlsx
@@ -690,6 +690,9 @@
       <c r="C31" t="str">
         <v>793_珍珠梅粉_undefined_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -748,7 +751,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0151520101055662055552051010105510551515510100</v>
+        <v>0151520101055662055552051010105510551515510105</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -694,9 +694,89 @@
         <v>5</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>323_木绣球_Green snowball viburnum_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>5</v>
+      </c>
+      <c r="C33" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>254_梦幻海葵_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>43_拉丝红_Spider Red_Gerbera L._20stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>6</v>
+      </c>
+      <c r="C37" t="str">
+        <v>125_绣球蓝_Hydrangea Light Blue S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F37" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F38" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F39" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>46_拉丝橙_Spider orange_Gerbera L._20stems</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>42_拉丝黄_Spider Yellow_Gerbera L._20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -751,7 +831,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0151520101055662055552051010105510551515510105</v>
+        <v>01515201010556620555520510101055105515155101051081051030303000</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-19.xlsx
@@ -773,6 +773,9 @@
       <c r="C41" t="str">
         <v>42_拉丝黄_Spider Yellow_Gerbera L._20stems</v>
       </c>
+      <c r="F41" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -831,7 +834,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01515201010556620555520510101055105515155101051081051030303000</v>
+        <v>01515201010556620555520510101055105515155101051081051030303005</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L46"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -777,9 +777,52 @@
         <v>5</v>
       </c>
     </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+      <c r="F42" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>41_拉丝白_Spider White_Gerbera L._20stems</v>
+      </c>
+      <c r="F43" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
+      </c>
+      <c r="F44" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>44_拉丝粉_Spider Pink_Gerbera L._20stems</v>
+      </c>
+      <c r="F45" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>7</v>
+      </c>
+      <c r="C46" t="str">
+        <v>764_芍药莎拉多头_undefined_undefined_10stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L46"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -834,7 +877,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01515201010556620555520510101055105515155101051081051030303005</v>
+        <v>01515201010556620555520510101055105515155101051081051030303005201010550</v>
       </c>
     </row>
   </sheetData>
